--- a/forms/trg/Formulir_TRG_food4nd.xlsx
+++ b/forms/trg/Formulir_TRG_food4nd.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,27 +925,27 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Andi Imam Arundhana Thahir, S.Gz., MPH</t>
+          <t>Prof Aminuddin Syam, S.KM., M.Kes., M.Med.Ed</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Department of Nutrition</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57189846867</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ulfah Najamuddin, S.Si., M.Kes</t>
+          <t>Andi Imam Arundhana Thahir, S.Gz., MPH</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -991,16 +991,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Dara Daygon</t>
+          <t>Ulfah Najamuddin, S.Si., M.Kes</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
-      <c r="E7" s="11" t="n"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Department of Nutrition</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
@@ -1020,19 +1024,15 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Yessy Kurniaty, SKM, M.Kes</t>
+          <t>Dr. Dara Daygon</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Public Health Study Program, Universitas Islam Negeri Alauddin</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
@@ -1053,24 +1053,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Risna Nurlia</t>
+          <t>Yessy Kurniaty, SKM, M.Kes</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Doctoral degree</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>A Quasi-Experimental Study on Fortified Tempeh on Fetal Growth in Indonesia</t>
-        </is>
-      </c>
+          <t>Public Health Study Program, Universitas Islam Negeri Alauddin</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1090,22 +1086,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Baiq Adinda Shabrina Suryati</t>
+          <t>Risna Nurlia</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Master's degree</t>
+          <t>Doctoral degree</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Acceptance Evaluation of Noodles Made from Yellow Pumpkin Leaves and Seaweed as an Alternative for Preventing Anemia in Adolescent Girls</t>
+          <t>A Quasi-Experimental Study on Fortified Tempeh on Fetal Growth in Indonesia</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1127,12 +1123,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Zaitun Khaerunnisa Sahril</t>
+          <t>Baiq Adinda Shabrina Suryati</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1142,7 +1138,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>The Health Impact of Noodles Made from Yellow Pumpkin Leaves and Seaweed as an Alternative on Anemia in Adolescent Girls</t>
+          <t>Acceptance Evaluation of Noodles Made from Yellow Pumpkin Leaves and Seaweed as an Alternative for Preventing Anemia in Adolescent Girls</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1164,12 +1160,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Besse Nurul Fadillah</t>
+          <t>Zaitun Khaerunnisa Sahril</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1179,7 +1175,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>The Effect of Yellow Pumpkin Seed (Cucurbita Moschata) Capsules on Dietary Intake and Hemoglobin Levels in Pregnant Women with Chronic Energy Deficiency</t>
+          <t>The Health Impact of Noodles Made from Yellow Pumpkin Leaves and Seaweed as an Alternative on Anemia in Adolescent Girls</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1201,12 +1197,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Rima Finarshy</t>
+          <t>Besse Nurul Fadillah</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1216,7 +1212,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>The Administration of a Combination of Anti-Tuberculosis Drugs (ATDs) and Yellow Pumpkin Seed Capsules on Hemoglobin Levels and Body Weight in Tuberculosis Patients in Majene Regency</t>
+          <t>The Effect of Yellow Pumpkin Seed (Cucurbita Moschata) Capsules on Dietary Intake and Hemoglobin Levels in Pregnant Women with Chronic Energy Deficiency</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1238,12 +1234,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Yanto</t>
+          <t>Rima Finarshy</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1253,7 +1249,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Effect of the Combination of Anti-Tuberculosis Drugs (ATDs) and Yellow Pumpkin Seed Capsules (Cucurbita moschata) on Changes in Bacterial Counts in the Sputum of TB Patients in Majene Regency</t>
+          <t>The Administration of a Combination of Anti-Tuberculosis Drugs (ATDs) and Yellow Pumpkin Seed Capsules on Hemoglobin Levels and Body Weight in Tuberculosis Patients in Majene Regency</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1273,10 +1269,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Yanto</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Effect of the Combination of Anti-Tuberculosis Drugs (ATDs) and Yellow Pumpkin Seed Capsules (Cucurbita moschata) on Changes in Bacterial Counts in the Sputum of TB Patients in Majene Regency</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1284,7 +1296,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1473,15 +1489,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
